--- a/Data/Indus_Valley.xlsx
+++ b/Data/Indus_Valley.xlsx
@@ -472,828 +472,828 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following crops was cultivated by the Indus people?</t>
+          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sugarcane</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
+          <t>Which animal figurine is found in large numbers at Indus sites?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following tools was not used by the Indus people?</t>
+          <t>Which Indus site is known for its water reservoir system?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Needles</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Axes</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fish hooks</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Why is the Indus script still undeciphered?</t>
+          <t>What was the main construction material in Indus Valley cities?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Too complex</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Sun-dried bricks</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>No grammar</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No surviving texts</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which site provides the earliest evidence of ploughed fields?</t>
+          <t>What material were seals of the Indus Valley generally made of?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What was the main construction material in Indus Valley cities?</t>
+          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun-dried bricks</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
+          <t>Which type of burial is found in Harappa?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Wooden coffin</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Assembly Hall</t>
+          <t>Brick chamber</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fire altar</t>
+          <t>Cave burial</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What was the script of the Indus Valley Civilization?</t>
+          <t>Which site had a circular platform possibly used for grain processing?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Fully deciphered</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Derived from Sanskrit</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arabic-derived</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What was used for weighing in the Indus Valley trade system?</t>
+          <t>Which god is believed to be depicted on seals in yogic posture?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metal bars</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Beads</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shells</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Indus Valley site was discovered during railway construction?</t>
+          <t>Which modern Indian state has the highest number of IVC sites?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which of these is a typical Harappan pottery style?</t>
+          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>1500–1000 BCE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Painted Grey</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Northern Black Polished</t>
+          <t>1000–500 BCE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ochre Colored</t>
+          <t>3000–2500 BCE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
+          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which animal is not found in any Indus Valley seal?</t>
+          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Soak pits</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Open drains only</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Cesspools</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which metal was not known to the Indus Valley people?</t>
+          <t>Which of the following crops was cultivated by the Indus people?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Sugarcane</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The weights used in Indus Valley were usually made of:</t>
+          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chert</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chert</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Indus Valley people?</t>
+          <t>What kind of jewelry was popular among the Indus people?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which of the following materials was used for toy-making?</t>
+          <t>What kind of urban planning was seen in Indus cities?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bone</t>
+          <t>Circular roads</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>No drainage</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Sloped streets</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
+          <t>What was used for weighing in the Indus Valley trade system?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Metal bars</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Beads</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rangpur</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Shells</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which modern Indian state has the highest number of IVC sites?</t>
+          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Rangpur</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which site had a circular platform possibly used for grain processing?</t>
+          <t>What was the approximate urban population of Mohenjo-daro?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which animal is prominently seen on many Indus seals?</t>
+          <t>Which modern tool is still similar to Harappan tools?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Loom</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Sickle</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Plough</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which is the westernmost Indus Valley site discovered?</t>
+          <t>Which of the following sites is located in present-day Pakistan?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Lothal</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>Mohenjo-daro</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Sutkagendor</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of the following sites is located in present-day Pakistan?</t>
+          <t>Which Indus Valley site was discovered during railway construction?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Harappa</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1336,316 +1336,316 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of the following is not found in Indus Valley sites?</t>
+          <t>Which Indus site was exclusively devoted to craft production?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Drainage system</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bead jewelry</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
+          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Assembly Hall</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Fire altar</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
+          <t>Which is the westernmost Indus Valley site discovered?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Soak pits</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Open drains only</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cesspools</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
+          <t>The Dancing Girl statue is made of which metal?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dancing girl</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bead necklace</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The major occupation of people in Chanhudaro was:</t>
+          <t>What type of government did the Indus Valley Civilization likely have?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The evidence of fire altars has been found at which site?</t>
+          <t>The Indus Valley Civilization was primarily based along which river?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which of the following sites is in Gujarat?</t>
+          <t>Which site provides the earliest evidence of ploughed fields?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Banawali</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Evidence of rice husk has been found at which Indus site?</t>
+          <t>Which of the following materials was used for toy-making?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Bone</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which site showed evidence of a possible signboard with Indus script?</t>
+          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>Lothal</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>Harappa</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Mohenjo-daro</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Dholavira</t>
@@ -1653,1519 +1653,1519 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which Indus site provides evidence of flood protection walls?</t>
+          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization was primarily based along which river?</t>
+          <t>Which site showed evidence of a possible signboard with Indus script?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
+          <t>Which of the following sites is in Gujarat?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Drainage</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
+          <t>Which Indus site provides evidence of flood protection walls?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>Lothal</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Harappa</t>
-        </is>
-      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
+          <t>Chanhudaro</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t>Dholavira</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Lothal</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
+          <t>The major occupation of people in Chanhudaro was:</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which structure was used for grain storage in Harappa?</t>
+          <t>Which animal is prominently seen on many Indus seals?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bathhouse</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which is the most urbanized and well-planned Harappan site?</t>
+          <t>The dockyard found at which site suggests maritime trade?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>Harappa</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Dholavira</t>
-        </is>
-      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
+          <t>The people of Indus Valley mainly worshipped which deity?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What material were seals of the Indus Valley generally made of?</t>
+          <t>The term “Harappan Civilization” is derived from which site?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chanhudaro was famous for which type of production?</t>
+          <t>The weights used in Indus Valley were usually made of:</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Chert</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granaries</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>Chert</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which was the largest site of the Indus Valley Civilization?</t>
+          <t>Which is the most urbanized and well-planned Harappan site?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Dholavira</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Rakhigarhi</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>Mohenjo-daro</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Dholavira</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Rakhigarhi</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>37</v>
+        <v>73</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
+          <t>Which artifact is considered a masterpiece of Indus art?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Pashupati Seal</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Terracotta Horse</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Script tablet</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
+          <t>Which of the following tools was not used by the Indus people?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Needles</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Axes</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Fish hooks</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The term “Harappan Civilization” is derived from which site?</t>
+          <t>What evidence suggests Harappan people were aware of dentistry?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Skeletons with gold teeth</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Toothbrush fossils</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Oral hygiene texts</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What type of government did the Indus Valley Civilization likely have?</t>
+          <t>Which of these is a typical Harappan pottery style?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Painted Grey</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Northern Black Polished</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Ochre Colored</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
+          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Persia</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The dockyard found at which site suggests maritime trade?</t>
+          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Brick-making</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Metal casting</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Dancing Girl statue is made of which metal?</t>
+          <t>Which structure was used for grain storage in Harappa?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Bathhouse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Great Bath is an important structure found at which Indus site?</t>
+          <t>Which important metal was absent in Harappan culture?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization belonged to which age?</t>
+          <t>Which was the largest site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Iron Age</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stone Age</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Neolithic</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What kind of jewelry was popular among the Indus people?</t>
+          <t>The Indus Valley Civilization belonged to which age?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Iron Age</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Stone Age</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Neolithic</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
+          <t>What was the main occupation of the Indus Valley people?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Brick-making</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Metal casting</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in large numbers at Indus sites?</t>
+          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Temple complex</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Terraced houses</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Pillared halls</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which god is believed to be depicted on seals in yogic posture?</t>
+          <t>Why is the Indus script still undeciphered?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Too complex</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>No grammar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>No surviving texts</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which modern tool is still similar to Harappan tools?</t>
+          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Loom</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Sickle</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plough</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
+          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1500–1000 BCE</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1000–500 BCE</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>3000–2500 BCE</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
+          <t>Chanhudaro was famous for which type of production?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Temple complex</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Terraced houses</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pillared halls</t>
+          <t>Granaries</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
+          <t>What kind of religion did the Indus Valley people follow?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Monotheism</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
+          <t>Which animal is not found in any Indus Valley seal?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which Indus site was exclusively devoted to craft production?</t>
+          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which important metal was absent in Harappan culture?</t>
+          <t>Evidence of rice husk has been found at which Indus site?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What was the approximate urban population of Mohenjo-daro?</t>
+          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which type of burial is found in Harappa?</t>
+          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Wooden coffin</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Brick chamber</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cave burial</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which artifact is considered a masterpiece of Indus art?</t>
+          <t>Which of the following is not found in Indus Valley sites?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Pashupati Seal</t>
+          <t>Drainage system</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Terracotta Horse</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Script tablet</t>
+          <t>Bead jewelry</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What kind of urban planning was seen in Indus cities?</t>
+          <t>The evidence of fire altars has been found at which site?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Circular roads</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>No drainage</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sloped streets</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The people of Indus Valley mainly worshipped which deity?</t>
+          <t>Which script was used by the Indus Valley people?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
+          <t>Which metal was not known to the Indus Valley people?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which material was used for making Indus Valley pottery?</t>
+          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Persia</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What kind of religion did the Indus Valley people follow?</t>
+          <t>What was the script of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Fully deciphered</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>Derived from Sanskrit</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Monotheism</t>
+          <t>Arabic-derived</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What evidence suggests Harappan people were aware of dentistry?</t>
+          <t>Which material was used for making Indus Valley pottery?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Skeletons with gold teeth</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Toothbrush fossils</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oral hygiene texts</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Indus site is known for its water reservoir system?</t>
+          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Dancing girl</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Bead necklace</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which script was used by the Indus Valley people?</t>
+          <t>The Great Bath is an important structure found at which Indus site?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/Indus_Valley.xlsx
+++ b/Data/Indus_Valley.xlsx
@@ -472,803 +472,803 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
+          <t>The evidence of fire altars has been found at which site?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Harappa</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Mohenjo-daro</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in large numbers at Indus sites?</t>
+          <t>Which material was used for making Indus Valley pottery?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which Indus site is known for its water reservoir system?</t>
+          <t>Which is the westernmost Indus Valley site discovered?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What was the main construction material in Indus Valley cities?</t>
+          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sun-dried bricks</t>
+          <t>Brick-making</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Metal casting</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What material were seals of the Indus Valley generally made of?</t>
+          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
+          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Assembly Hall</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Fire altar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which type of burial is found in Harappa?</t>
+          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wooden coffin</t>
+          <t>1500–1000 BCE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Brick chamber</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>1000–500 BCE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cave burial</t>
+          <t>3000–2500 BCE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which site had a circular platform possibly used for grain processing?</t>
+          <t>What kind of urban planning was seen in Indus cities?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Circular roads</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>No drainage</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Sloped streets</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which god is believed to be depicted on seals in yogic posture?</t>
+          <t>Which is the most urbanized and well-planned Harappan site?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which modern Indian state has the highest number of IVC sites?</t>
+          <t>Which type of burial is found in Harappa?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Wooden coffin</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Brick chamber</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Cave burial</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
+          <t>Which of the following crops was cultivated by the Indus people?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1500–1000 BCE</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Sugarcane</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1000–500 BCE</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3000–2500 BCE</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
+          <t>Which site provides the earliest evidence of ploughed fields?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Drainage</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
+          <t>Which Indus site provides evidence of flood protection walls?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Soak pits</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Open drains only</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cesspools</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which of the following crops was cultivated by the Indus people?</t>
+          <t>The weights used in Indus Valley were usually made of:</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sugarcane</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Chert</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Chert</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
+          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What kind of jewelry was popular among the Indus people?</t>
+          <t>Which of these is a typical Harappan pottery style?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Painted Grey</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Northern Black Polished</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Ochre Colored</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What kind of urban planning was seen in Indus cities?</t>
+          <t>Which modern Indian state has the highest number of IVC sites?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Circular roads</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No drainage</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sloped streets</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What was used for weighing in the Indus Valley trade system?</t>
+          <t>The Indus Valley Civilization was primarily based along which river?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Metal bars</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Beads</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shells</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
+          <t>Which artifact is considered a masterpiece of Indus art?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Pashupati Seal</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rangpur</t>
+          <t>Terracotta Horse</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Script tablet</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What was the approximate urban population of Mohenjo-daro?</t>
+          <t>What was the script of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>Fully deciphered</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Derived from Sanskrit</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>Arabic-derived</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which modern tool is still similar to Harappan tools?</t>
+          <t>Which Indus site is known for its water reservoir system?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loom</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sickle</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plough</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which of the following sites is located in present-day Pakistan?</t>
+          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which Indus Valley site was discovered during railway construction?</t>
+          <t>The dockyard found at which site suggests maritime trade?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1283,161 +1283,161 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which foreign civilization had trade relations with the Indus people?</t>
+          <t>What kind of jewelry was popular among the Indus people?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mesopotamian</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mesopotamian</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which Indus site was exclusively devoted to craft production?</t>
+          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Dancing girl</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Bead necklace</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
+          <t>What material were seals of the Indus Valley generally made of?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Assembly Hall</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fire altar</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which is the westernmost Indus Valley site discovered?</t>
+          <t>Which modern tool is still similar to Harappan tools?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Loom</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Sickle</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Plough</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1480,93 +1480,93 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What type of government did the Indus Valley Civilization likely have?</t>
+          <t>What kind of religion did the Indus Valley people follow?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Monotheism</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization was primarily based along which river?</t>
+          <t>Which of the following sites is located in present-day Pakistan?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which site provides the earliest evidence of ploughed fields?</t>
+          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1576,383 +1576,383 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which of the following materials was used for toy-making?</t>
+          <t>Which animal is prominently seen on many Indus seals?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bone</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
+          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Soak pits</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Open drains only</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Cesspools</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
+          <t>Which foreign civilization had trade relations with the Indus people?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Mesopotamian</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Mesopotamian</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which site showed evidence of a possible signboard with Indus script?</t>
+          <t>Chanhudaro was famous for which type of production?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Granaries</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which of the following sites is in Gujarat?</t>
+          <t>Which site showed evidence of a possible signboard with Indus script?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Harappa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Mohenjo-daro</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Kalibangan</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Indus site provides evidence of flood protection walls?</t>
+          <t>What was used for weighing in the Indus Valley trade system?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Metal bars</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Beads</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Shells</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The major occupation of people in Chanhudaro was:</t>
+          <t>Which important metal was absent in Harappan culture?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which animal is prominently seen on many Indus seals?</t>
+          <t>Which of the following tools was not used by the Indus people?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Needles</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Axes</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Fish hooks</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The dockyard found at which site suggests maritime trade?</t>
+          <t>Which of the following is not found in Indus Valley sites?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Drainage system</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Bead jewelry</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>The people of Indus Valley mainly worshipped which deity?</t>
+          <t>Which structure was used for grain storage in Harappa?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Bathhouse</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The term “Harappan Civilization” is derived from which site?</t>
+          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1977,1195 +1977,1195 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The weights used in Indus Valley were usually made of:</t>
+          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chert</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chert</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is the most urbanized and well-planned Harappan site?</t>
+          <t>Which animal is not found in any Indus Valley seal?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which artifact is considered a masterpiece of Indus art?</t>
+          <t>The term “Harappan Civilization” is derived from which site?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pashupati Seal</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Terracotta Horse</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Script tablet</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following tools was not used by the Indus people?</t>
+          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Needles</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Axes</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Rangpur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fish hooks</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What evidence suggests Harappan people were aware of dentistry?</t>
+          <t>Which Indus Valley site was discovered during railway construction?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Skeletons with gold teeth</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Toothbrush fossils</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oral hygiene texts</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which of these is a typical Harappan pottery style?</t>
+          <t>The major occupation of people in Chanhudaro was:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Painted Grey</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Northern Black Polished</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ochre Colored</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
+          <t>The Indus Valley Civilization belonged to which age?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Iron Age</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Stone Age</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Neolithic</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
+          <t>Which metal was not known to the Indus Valley people?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Brick-making</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Metal casting</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which structure was used for grain storage in Harappa?</t>
+          <t>What type of government did the Indus Valley Civilization likely have?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bathhouse</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which important metal was absent in Harappan culture?</t>
+          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which was the largest site of the Indus Valley Civilization?</t>
+          <t>Which god is believed to be depicted on seals in yogic posture?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization belonged to which age?</t>
+          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Iron Age</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stone Age</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Neolithic</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Indus Valley people?</t>
+          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Temple complex</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Terraced houses</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Pillared halls</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
+          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Temple complex</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Terraced houses</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pillared halls</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Why is the Indus script still undeciphered?</t>
+          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Too complex</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>No grammar</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>No surviving texts</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
+          <t>The Great Bath is an important structure found at which Indus site?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
+          <t>Which was the largest site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
+          <t>Mohenjo-daro</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
           <t>Lothal</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Kalibangan</t>
-        </is>
-      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Chanhudaro was famous for which type of production?</t>
+          <t>What was the main occupation of the Indus Valley people?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granaries</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What kind of religion did the Indus Valley people follow?</t>
+          <t>Why is the Indus script still undeciphered?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>Too complex</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>No grammar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Monotheism</t>
+          <t>No surviving texts</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which animal is not found in any Indus Valley seal?</t>
+          <t>Which of the following materials was used for toy-making?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Bone</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
+          <t>The people of Indus Valley mainly worshipped which deity?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Evidence of rice husk has been found at which Indus site?</t>
+          <t>What was the main construction material in Indus Valley cities?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Sun-dried bricks</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
+          <t>Which script was used by the Indus Valley people?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
+          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which of the following is not found in Indus Valley sites?</t>
+          <t>Which of the following sites is in Gujarat?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Drainage system</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bead jewelry</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The evidence of fire altars has been found at which site?</t>
+          <t>What evidence suggests Harappan people were aware of dentistry?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Skeletons with gold teeth</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Toothbrush fossils</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Oral hygiene texts</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which script was used by the Indus Valley people?</t>
+          <t>What was the approximate urban population of Mohenjo-daro?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which metal was not known to the Indus Valley people?</t>
+          <t>Which animal figurine is found in large numbers at Indus sites?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
+          <t>Which site had a circular platform possibly used for grain processing?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persia</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What was the script of the Indus Valley Civilization?</t>
+          <t>Which Indus site was exclusively devoted to craft production?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Fully deciphered</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Derived from Sanskrit</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Arabic-derived</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which material was used for making Indus Valley pottery?</t>
+          <t>Evidence of rice husk has been found at which Indus site?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
+          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dancing girl</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bead necklace</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The Great Bath is an important structure found at which Indus site?</t>
+          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Persia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/Indus_Valley.xlsx
+++ b/Data/Indus_Valley.xlsx
@@ -472,57 +472,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The evidence of fire altars has been found at which site?</t>
+          <t>Which animal is prominently seen on many Indus seals?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which material was used for making Indus Valley pottery?</t>
+          <t>The Dancing Girl statue is made of which metal?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -532,676 +532,676 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which is the westernmost Indus Valley site discovered?</t>
+          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
+          <t>Which of the following sites is in Gujarat?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brick-making</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Metal casting</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
+          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Persia</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
+          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Assembly Hall</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fire altar</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
+          <t>Which of the following tools was not used by the Indus people?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1500–1000 BCE</t>
+          <t>Needles</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Axes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1000–500 BCE</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3000–2500 BCE</t>
+          <t>Fish hooks</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What kind of urban planning was seen in Indus cities?</t>
+          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Circular roads</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>No drainage</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sloped streets</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>62</v>
+        <v>14</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which is the most urbanized and well-planned Harappan site?</t>
+          <t>Chanhudaro was famous for which type of production?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Granaries</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which type of burial is found in Harappa?</t>
+          <t>Which of the following crops was cultivated by the Indus people?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wooden coffin</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Brick chamber</t>
+          <t>Sugarcane</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cave burial</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which of the following crops was cultivated by the Indus people?</t>
+          <t>The term “Harappan Civilization” is derived from which site?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sugarcane</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which site provides the earliest evidence of ploughed fields?</t>
+          <t>Which Indus site was exclusively devoted to craft production?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Lothal</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Chanhudaro</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Ropar</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Banawali</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Surkotada</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Indus site provides evidence of flood protection walls?</t>
+          <t>Which god is believed to be depicted on seals in yogic posture?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>The weights used in Indus Valley were usually made of:</t>
+          <t>What kind of religion did the Indus Valley people follow?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chert</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Monotheism</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chert</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
+          <t>Which modern tool is still similar to Harappan tools?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Loom</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Sickle</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Plough</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which of these is a typical Harappan pottery style?</t>
+          <t>Which of the following sites is located in present-day Pakistan?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Painted Grey</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Northern Black Polished</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ochre Colored</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which modern Indian state has the highest number of IVC sites?</t>
+          <t>Which type of burial is found in Harappa?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Wooden coffin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Brick chamber</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Cave burial</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization was primarily based along which river?</t>
+          <t>The Indus Valley Civilization belonged to which age?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Iron Age</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Stone Age</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Neolithic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which artifact is considered a masterpiece of Indus art?</t>
+          <t>Why is the Indus script still undeciphered?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Too complex</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pashupati Seal</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Terracotta Horse</t>
+          <t>No grammar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Script tablet</t>
+          <t>No surviving texts</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What was the script of the Indus Valley Civilization?</t>
+          <t>Which of the following materials was used for toy-making?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Bone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fully deciphered</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Derived from Sanskrit</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Arabic-derived</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Indus site is known for its water reservoir system?</t>
+          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1211,521 +1211,521 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Rangpur</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
+          <t>What was the approximate urban population of Mohenjo-daro?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Drainage</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The dockyard found at which site suggests maritime trade?</t>
+          <t>What was the script of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Fully deciphered</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Derived from Sanskrit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Arabic-derived</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What kind of jewelry was popular among the Indus people?</t>
+          <t>The evidence of fire altars has been found at which site?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
+          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Temple complex</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dancing girl</t>
+          <t>Terraced houses</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bead necklace</t>
+          <t>Pillared halls</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What material were seals of the Indus Valley generally made of?</t>
+          <t>Which of the following is not found in Indus Valley sites?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Drainage system</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Bead jewelry</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which modern tool is still similar to Harappan tools?</t>
+          <t>Which Indus site is known for its water reservoir system?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Loom</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sickle</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Plough</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Dancing Girl statue is made of which metal?</t>
+          <t>The major occupation of people in Chanhudaro was:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What kind of religion did the Indus Valley people follow?</t>
+          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>Dancing girl</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monotheism</t>
+          <t>Bead necklace</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which of the following sites is located in present-day Pakistan?</t>
+          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Rakhigarhi</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lothal</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Mohenjo-daro</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
+          <t>What kind of jewelry was popular among the Indus people?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which animal is prominently seen on many Indus seals?</t>
+          <t>The Great Bath is an important structure found at which Indus site?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
+          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Soak pits</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Open drains only</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cesspools</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which foreign civilization had trade relations with the Indus people?</t>
+          <t>Which modern Indian state has the highest number of IVC sites?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mesopotamian</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mesopotamian</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chanhudaro was famous for which type of production?</t>
+          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>1500–1000 BCE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>1000–500 BCE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granaries</t>
+          <t>3000–2500 BCE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1768,304 +1768,304 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What was used for weighing in the Indus Valley trade system?</t>
+          <t>What kind of urban planning was seen in Indus cities?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Metal bars</t>
+          <t>Circular roads</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Beads</t>
+          <t>No drainage</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shells</t>
+          <t>Sloped streets</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which important metal was absent in Harappan culture?</t>
+          <t>Which Indus Valley site was discovered during railway construction?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of the following tools was not used by the Indus people?</t>
+          <t>What material were seals of the Indus Valley generally made of?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Needles</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Axes</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fish hooks</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which of the following is not found in Indus Valley sites?</t>
+          <t>Which site had a circular platform possibly used for grain processing?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Drainage system</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bead jewelry</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which structure was used for grain storage in Harappa?</t>
+          <t>Which metal was not known to the Indus Valley people?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bathhouse</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
+          <t>Which is the westernmost Indus Valley site discovered?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
+          <t>What was the main construction material in Indus Valley cities?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Sun-dried bricks</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which animal is not found in any Indus Valley seal?</t>
+          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The term “Harappan Civilization” is derived from which site?</t>
+          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2075,393 +2075,393 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
+          <t>Which important metal was absent in Harappan culture?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rangpur</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>70</v>
+        <v>17</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which Indus Valley site was discovered during railway construction?</t>
+          <t>The people of Indus Valley mainly worshipped which deity?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The major occupation of people in Chanhudaro was:</t>
+          <t>Which animal is not found in any Indus Valley seal?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization belonged to which age?</t>
+          <t>Which is the most urbanized and well-planned Harappan site?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Iron Age</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stone Age</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neolithic</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which metal was not known to the Indus Valley people?</t>
+          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What type of government did the Indus Valley Civilization likely have?</t>
+          <t>Which artifact is considered a masterpiece of Indus art?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Pashupati Seal</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Terracotta Horse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Script tablet</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
+          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Assembly Hall</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Fire altar</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which god is believed to be depicted on seals in yogic posture?</t>
+          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Soak pits</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Open drains only</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Cesspools</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
+          <t>Which script was used by the Indus Valley people?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
+          <t>Which material was used for making Indus Valley pottery?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Temple complex</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Terraced houses</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pillared halls</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
+          <t>Which Indus site provides evidence of flood protection walls?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2471,701 +2471,701 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
+          <t>What was used for weighing in the Indus Valley trade system?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Metal bars</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Beads</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Shells</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>The Great Bath is an important structure found at which Indus site?</t>
+          <t>The weights used in Indus Valley were usually made of:</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Chert</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Chert</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which was the largest site of the Indus Valley Civilization?</t>
+          <t>The Indus Valley Civilization was primarily based along which river?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Indus Valley people?</t>
+          <t>Which was the largest site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Why is the Indus script still undeciphered?</t>
+          <t>The dockyard found at which site suggests maritime trade?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Too complex</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>No grammar</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>No surviving texts</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which of the following materials was used for toy-making?</t>
+          <t>Which of these is a typical Harappan pottery style?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bone</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Painted Grey</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Northern Black Polished</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Ochre Colored</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The people of Indus Valley mainly worshipped which deity?</t>
+          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What was the main construction material in Indus Valley cities?</t>
+          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Sun-dried bricks</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which script was used by the Indus Valley people?</t>
+          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
+          <t>Which animal figurine is found in large numbers at Indus sites?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which of the following sites is in Gujarat?</t>
+          <t>What evidence suggests Harappan people were aware of dentistry?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Skeletons with gold teeth</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Toothbrush fossils</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Oral hygiene texts</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What evidence suggests Harappan people were aware of dentistry?</t>
+          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Skeletons with gold teeth</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Brick-making</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Toothbrush fossils</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Oral hygiene texts</t>
+          <t>Metal casting</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What was the approximate urban population of Mohenjo-daro?</t>
+          <t>What type of government did the Indus Valley Civilization likely have?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in large numbers at Indus sites?</t>
+          <t>Evidence of rice husk has been found at which Indus site?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which site had a circular platform possibly used for grain processing?</t>
+          <t>Which structure was used for grain storage in Harappa?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Bathhouse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which Indus site was exclusively devoted to craft production?</t>
+          <t>What was the main occupation of the Indus Valley people?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Evidence of rice husk has been found at which Indus site?</t>
+          <t>Which foreign civilization had trade relations with the Indus people?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Mesopotamian</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Mesopotamian</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
+          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
+          <t>Which site provides the earliest evidence of ploughed fields?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Persia</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>

--- a/Data/Indus_Valley.xlsx
+++ b/Data/Indus_Valley.xlsx
@@ -472,2052 +472,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which animal is prominently seen on many Indus seals?</t>
+          <t>Which animal figurine is found in large numbers at Indus sites?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Lion</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>Horse</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Unicorn</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Peacock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Dancing Girl statue is made of which metal?</t>
+          <t>Which animal is not found in any Indus Valley seal?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
+          <t>Which Indus site provides evidence of flood protection walls?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which of the following sites is in Gujarat?</t>
+          <t>Which of the following crops was cultivated by the Indus people?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Sugarcane</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Wheat and Barley</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
+          <t>Which structure indicates ritual bathing in the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persia</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Indus Valley</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
+          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which of the following tools was not used by the Indus people?</t>
+          <t>The term 'Meluhha' used in Mesopotamian records refers to:</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Needles</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Axes</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fish hooks</t>
+          <t>Persia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iron plough</t>
+          <t>Indus Valley</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
+          <t>Which site had a circular platform possibly used for grain processing?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>Mohenjo-daro</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Lothal</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Harappa</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Lothal</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Surkotada</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chanhudaro was famous for which type of production?</t>
+          <t>Which was the largest site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granaries</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bead-making</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which of the following crops was cultivated by the Indus people?</t>
+          <t>Which script was used by the Indus Valley people?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sugarcane</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Wheat and Barley</t>
+          <t>Indus script</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The term “Harappan Civilization” is derived from which site?</t>
+          <t>Which site provides the earliest evidence of ploughed fields?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>Banawali</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>Kalibangan</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Mohenjo-daro</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Indus site was exclusively devoted to craft production?</t>
+          <t>Which of the following sites is in Gujarat?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Mohenjo-daro</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Lothal</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Chanhudaro</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ropar</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which god is believed to be depicted on seals in yogic posture?</t>
+          <t>What kind of religion did the Indus Valley people follow?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indra</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Temple worship</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Monotheism</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Pashupati)</t>
+          <t>Polytheistic nature worship</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What kind of religion did the Indus Valley people follow?</t>
+          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>1500–1000 BCE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Temple worship</t>
+          <t>1000–500 BCE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monotheism</t>
+          <t>3000–2500 BCE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polytheistic nature worship</t>
+          <t>2600–1900 BCE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which modern tool is still similar to Harappan tools?</t>
+          <t>Which metal was not known to the Indus Valley people?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Loom</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sickle</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plough</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Potter’s wheel</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which of the following sites is located in present-day Pakistan?</t>
+          <t>The major occupation of people in Chanhudaro was:</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Farming</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Bead making</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which type of burial is found in Harappa?</t>
+          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wooden coffin</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Brick chamber</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>Rangpur</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Cave burial</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Extended and pot burial</t>
+          <t>Daimabad</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization belonged to which age?</t>
+          <t>Which of the following materials was used for toy-making?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Bone</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Iron Age</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stone Age</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Neolithic</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bronze Age</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Why is the Indus script still undeciphered?</t>
+          <t>The dockyard found at which site suggests maritime trade?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Too complex</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>No grammar</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>No surviving texts</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No bilingual text</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which of the following materials was used for toy-making?</t>
+          <t>Which of the following is not found in Indus Valley sites?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bone</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Drainage system</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Bead jewelry</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which was the southernmost site of the Indus Valley Civilization?</t>
+          <t>Which structure was used for grain storage in Harappa?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rangpur</t>
+          <t>Bathhouse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Daimabad</t>
+          <t>Granary</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What was the approximate urban population of Mohenjo-daro?</t>
+          <t>Chanhudaro was famous for which type of production?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>Pottery</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>Granaries</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>Bead-making</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What was the script of the Indus Valley Civilization?</t>
+          <t>Which foreign civilization had trade relations with the Indus people?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fully deciphered</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Derived from Sanskrit</t>
+          <t>Mesopotamian</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arabic-derived</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Still undeciphered</t>
+          <t>Mesopotamian</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The evidence of fire altars has been found at which site?</t>
+          <t>Which material was used for making Indus Valley pottery?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Bricks</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Glass</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
+          <t>Which modern tool is still similar to Harappan tools?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Loom</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Temple complex</t>
+          <t>Sickle</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Terraced houses</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pillared halls</t>
+          <t>Plough</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Citadel and lower town</t>
+          <t>Potter’s wheel</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which of the following is not found in Indus Valley sites?</t>
+          <t>Which of the following sites is located in present-day Pakistan?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pottery</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Drainage system</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bead jewelry</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which Indus site is known for its water reservoir system?</t>
+          <t>What kind of urban planning was seen in Indus cities?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Circular roads</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>No drainage</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Sloped streets</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Grid pattern</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The major occupation of people in Chanhudaro was:</t>
+          <t>Which of the following tools was not used by the Indus people?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Farming</t>
+          <t>Needles</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Axes</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Fish hooks</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bead making</t>
+          <t>Iron plough</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
+          <t>Which is the most urbanized and well-planned Harappan site?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dancing girl</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bead necklace</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pashupati seal</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which Indus Valley site is closest to the Arabian Sea?</t>
+          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Citadel</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Drainage</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Dockyard</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Reservoirs</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What kind of jewelry was popular among the Indus people?</t>
+          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Beads and bangles</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Great Bath is an important structure found at which Indus site?</t>
+          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Soak pits</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Open drains only</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Cesspools</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Underground sewers</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
+          <t>Which Indus site is known for its water reservoir system?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pig</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which modern Indian state has the highest number of IVC sites?</t>
+          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Assembly Hall</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Fire altar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Six-roomed building</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What is the approximate time period of the mature phase of the Indus Valley Civilization?</t>
+          <t>What type of government did the Indus Valley Civilization likely have?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1500–1000 BCE</t>
+          <t>Monarchy</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1000–500 BCE</t>
+          <t>Theocracy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3000–2500 BCE</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2600–1900 BCE</t>
+          <t>Centralized or unknown</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which site showed evidence of a possible signboard with Indus script?</t>
+          <t>What was the script of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Fully deciphered</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Derived from Sanskrit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Arabic-derived</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Still undeciphered</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What kind of urban planning was seen in Indus cities?</t>
+          <t>What was the main occupation of the Indus Valley people?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Circular roads</t>
+          <t>Hunting</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>No drainage</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Fishing</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sloped streets</t>
+          <t>Metalwork</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Grid pattern</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which Indus Valley site was discovered during railway construction?</t>
+          <t>What kind of jewelry was popular among the Indus people?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Beads and bangles</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What material were seals of the Indus Valley generally made of?</t>
+          <t>The Indus Valley Civilization was primarily based along which river?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Steatite</t>
+          <t>Indus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which site had a circular platform possibly used for grain processing?</t>
+          <t>Which site showed evidence of a possible signboard with Indus script?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>Mohenjo-daro</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which metal was not known to the Indus Valley people?</t>
+          <t>Which type of burial is found in Harappa?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Wooden coffin</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Brick chamber</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Cave burial</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Extended and pot burial</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which is the westernmost Indus Valley site discovered?</t>
+          <t>Which Indus site was exclusively devoted to craft production?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Chanhudaro</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What was the main construction material in Indus Valley cities?</t>
+          <t>What material were seals of the Indus Valley generally made of?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Terracotta</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Steatite</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Wood</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Sun-dried bricks</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Stone</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Burnt bricks</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Burnt bricks</t>
+          <t>Steatite</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
+          <t>Which was the first discovered site of the Indus Valley Civilization?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>Harappa</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Mohenjo-daro</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Lothal</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Dholavira</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>Harappa</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Kalibangan</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Dholavira</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Lothal</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
+          <t>Which important metal was absent in Harappan culture?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which important metal was absent in Harappan culture?</t>
+          <t>Why is the Indus script still undeciphered?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Too complex</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>No grammar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>No surviving texts</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>No bilingual text</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The people of Indus Valley mainly worshipped which deity?</t>
+          <t>Which is the westernmost Indus Valley site discovered?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vishnu</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brahma</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Agni</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Shiva (Proto-Shiva)</t>
+          <t>Sutkagendor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which animal is not found in any Indus Valley seal?</t>
+          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Unicorn</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which is the most urbanized and well-planned Harappan site?</t>
+          <t>Which modern Indian state has the highest number of IVC sites?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which feature was unique to Dholavira among Indus Valley sites?</t>
+          <t>Which Indus Valley site provides evidence of burial along with animal sacrifices?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Drainage</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dockyard</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Reservoirs</t>
+          <t>Rakhigarhi</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which artifact is considered a masterpiece of Indus art?</t>
+          <t>The people of Indus Valley mainly worshipped which deity?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pashupati Seal</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Terracotta Horse</t>
+          <t>Brahma</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Script tablet</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dancing Girl</t>
+          <t>Shiva (Proto-Shiva)</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which structure at Mohenjo-daro is believed to be a public granary?</t>
+          <t>Which of these is a typical Harappan pottery style?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Great Bath</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Assembly Hall</t>
+          <t>Painted Grey</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Northern Black Polished</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fire altar</t>
+          <t>Ochre Colored</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Six-roomed building</t>
+          <t>Black-on-red</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which method was used by the Indus Valley people to drain wastewater?</t>
+          <t>What was the main construction material in Indus Valley cities?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Soak pits</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Sun-dried bricks</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Open drains only</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cesspools</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Underground sewers</t>
+          <t>Burnt bricks</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which script was used by the Indus Valley people?</t>
+          <t>The Great Bath is an important structure found at which Indus site?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Indus script</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which material was used for making Indus Valley pottery?</t>
+          <t>Which of these is a unique feature of Mohenjo-daro’s architecture?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bricks</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Temple complex</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Terraced houses</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Glass</t>
+          <t>Pillared halls</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Terracotta</t>
+          <t>Citadel and lower town</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Indus site provides evidence of flood protection walls?</t>
+          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>Surkotada</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Lothal</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Dholavira</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Chanhudaro</t>
-        </is>
-      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What was used for weighing in the Indus Valley trade system?</t>
+          <t>The Dancing Girl statue is made of which metal?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Metal bars</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Beads</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Terracotta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shells</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Stone weights</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2560,103 +2560,103 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Indus Valley Civilization was primarily based along which river?</t>
+          <t>Which of these sites shows evidence of both burial and post-cremation urn burials?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Dholavira</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Indus</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which was the largest site of the Indus Valley Civilization?</t>
+          <t>What evidence suggests Harappan people were aware of dentistry?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Skeletons with gold teeth</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Toothbrush fossils</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Oral hygiene texts</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Tooth drills</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>The dockyard found at which site suggests maritime trade?</t>
+          <t>Evidence of rice husk has been found at which Indus site?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Rakhigarhi</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Kalibangan</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Lothal</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>Harappa</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Kalibangan</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Lothal</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ropar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2668,124 +2668,124 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which of these is a typical Harappan pottery style?</t>
+          <t>The term “Harappan Civilization” is derived from which site?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Painted Grey</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Northern Black Polished</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ochre Colored</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Black-on-red</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
+          <t>Which animal is prominently seen on many Indus seals?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Textiles</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Timber</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Unicorn</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which site has yielded evidence of a horse bone, though disputed?</t>
+          <t>Which god is believed to be depicted on seals in yogic posture?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Indra</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Vishnu</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dholavira</t>
+          <t>Agni</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Shiva (Proto-Pashupati)</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which site shows the earliest evidence of a ploughed agricultural field?</t>
+          <t>Which archaeological site provides evidence of both Harappan and Vedic cultures?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Ropar</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2795,377 +2795,377 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mohenjo-daro</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which animal figurine is found in large numbers at Indus sites?</t>
+          <t>What was the approximate urban population of Mohenjo-daro?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Peacock</t>
+          <t>100,000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What evidence suggests Harappan people were aware of dentistry?</t>
+          <t>The evidence of fire altars has been found at which site?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Skeletons with gold teeth</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Toothbrush fossils</t>
+          <t>Mohenjo-daro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oral hygiene texts</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tooth drills</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
+          <t>Which Indus Valley site was discovered during railway construction?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Brick-making</t>
+          <t>Kalibangan</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Banawali</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Metal casting</t>
+          <t>Surkotada</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Shell-working</t>
+          <t>Harappa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>65</v>
+        <v>16</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What type of government did the Indus Valley Civilization likely have?</t>
+          <t>The Indus Valley Civilization belonged to which age?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Monarchy</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Iron Age</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Theocracy</t>
+          <t>Stone Age</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Neolithic</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Centralized or unknown</t>
+          <t>Bronze Age</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Evidence of rice husk has been found at which Indus site?</t>
+          <t>Which artifact is considered evidence of early yoga in the Indus Valley?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Great Bath</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Dancing girl</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Harappa</t>
+          <t>Bead necklace</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Pashupati seal</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which structure was used for grain storage in Harappa?</t>
+          <t>Which craft is associated with Nageshwar, an Indus Valley site?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Citadel</t>
+          <t>Brick-making</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bathhouse</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Metal casting</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Granary</t>
+          <t>Shell-working</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3</v>
+        <v>69</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What was the main occupation of the Indus Valley people?</t>
+          <t>Which animal figurine is found in terracotta form in Harappan sites?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hunting</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Pig</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Metalwork</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which foreign civilization had trade relations with the Indus people?</t>
+          <t>Which artifact is considered a masterpiece of Indus art?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Pashupati Seal</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mesopotamian</t>
+          <t>Terracotta Horse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Script tablet</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mesopotamian</t>
+          <t>Dancing Girl</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Harappan site was located in Baluchistan (now Pakistan)?</t>
+          <t>What was used for weighing in the Indus Valley trade system?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Metal bars</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Beads</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rakhigarhi</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Chanhudaro</t>
+          <t>Shells</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sutkagendor</t>
+          <t>Stone weights</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which site provides the earliest evidence of ploughed fields?</t>
+          <t>Which of the following was a key export of Indus Valley to Mesopotamia?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ropar</t>
+          <t>Textiles</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Banawali</t>
+          <t>Timber</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Surkotada</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kalibangan</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
